--- a/artfynd/A 40059-2025 artfynd.xlsx
+++ b/artfynd/A 40059-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -905,6 +905,126 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128628492</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57682</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stenformation, Ö om Funtamosse, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>343122</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6435173</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Torr granstubbe med spillkråkehack, i spännande stenformation.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40059-2025 artfynd.xlsx
+++ b/artfynd/A 40059-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1025,6 +1025,360 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128642834</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56991</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100065</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Trana</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Grus grus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>sträckande S</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Funtamosse öster 2, Risveden, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>343152</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6435175</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>3 flockar</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lennart Gustafson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lennart Gustafson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128642757</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57845</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Funtamosse öster 1, Risveden, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>343076</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6435192</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lennart Gustafson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lennart Gustafson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128642844</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58362</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Funtamosse öster 2, Risveden, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>343152</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6435175</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lennart Gustafson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lennart Gustafson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40059-2025 artfynd.xlsx
+++ b/artfynd/A 40059-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128602400</v>
       </c>
       <c r="B2" t="n">
-        <v>96173</v>
+        <v>96179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128606867</v>
       </c>
       <c r="B3" t="n">
-        <v>56876</v>
+        <v>56880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>128628492</v>
       </c>
       <c r="B4" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>128642834</v>
       </c>
       <c r="B5" t="n">
-        <v>56991</v>
+        <v>56995</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>128642757</v>
       </c>
       <c r="B6" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128642844</v>
       </c>
       <c r="B7" t="n">
-        <v>58362</v>
+        <v>58366</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 40059-2025 artfynd.xlsx
+++ b/artfynd/A 40059-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128602400</v>
       </c>
       <c r="B2" t="n">
-        <v>96179</v>
+        <v>96185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40059-2025 artfynd.xlsx
+++ b/artfynd/A 40059-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128602400</v>
       </c>
       <c r="B2" t="n">
-        <v>96185</v>
+        <v>96187</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40059-2025 artfynd.xlsx
+++ b/artfynd/A 40059-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128602400</v>
       </c>
       <c r="B2" t="n">
-        <v>96187</v>
+        <v>96188</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1379,6 +1379,118 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128806558</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97463</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Fuktdråg 2, Ö om Funtamosse, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>343062</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6435187</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40059-2025 artfynd.xlsx
+++ b/artfynd/A 40059-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128602400</v>
       </c>
       <c r="B2" t="n">
-        <v>96188</v>
+        <v>96215</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128606867</v>
       </c>
       <c r="B3" t="n">
-        <v>56880</v>
+        <v>56907</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>128628492</v>
       </c>
       <c r="B4" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>128642834</v>
       </c>
       <c r="B5" t="n">
-        <v>56995</v>
+        <v>57022</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>128642757</v>
       </c>
       <c r="B6" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128642844</v>
       </c>
       <c r="B7" t="n">
-        <v>58366</v>
+        <v>58393</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>128806558</v>
       </c>
       <c r="B8" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 40059-2025 artfynd.xlsx
+++ b/artfynd/A 40059-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128602400</v>
       </c>
       <c r="B2" t="n">
-        <v>96215</v>
+        <v>96221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>128806558</v>
       </c>
       <c r="B8" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 40059-2025 artfynd.xlsx
+++ b/artfynd/A 40059-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128602400</v>
       </c>
       <c r="B2" t="n">
-        <v>96221</v>
+        <v>96228</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>128806558</v>
       </c>
       <c r="B8" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 40059-2025 artfynd.xlsx
+++ b/artfynd/A 40059-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128602400</v>
       </c>
       <c r="B2" t="n">
-        <v>96228</v>
+        <v>96232</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128606867</v>
       </c>
       <c r="B3" t="n">
-        <v>56907</v>
+        <v>56910</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>128628492</v>
       </c>
       <c r="B4" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>128642834</v>
       </c>
       <c r="B5" t="n">
-        <v>57022</v>
+        <v>57025</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>128642757</v>
       </c>
       <c r="B6" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128642844</v>
       </c>
       <c r="B7" t="n">
-        <v>58393</v>
+        <v>58397</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>128806558</v>
       </c>
       <c r="B8" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 40059-2025 artfynd.xlsx
+++ b/artfynd/A 40059-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128602400</v>
       </c>
       <c r="B2" t="n">
-        <v>96232</v>
+        <v>96239</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128606867</v>
       </c>
       <c r="B3" t="n">
-        <v>56910</v>
+        <v>56913</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>128628492</v>
       </c>
       <c r="B4" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>128642834</v>
       </c>
       <c r="B5" t="n">
-        <v>57025</v>
+        <v>57028</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>128642757</v>
       </c>
       <c r="B6" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128642844</v>
       </c>
       <c r="B7" t="n">
-        <v>58397</v>
+        <v>58400</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>128806558</v>
       </c>
       <c r="B8" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 40059-2025 artfynd.xlsx
+++ b/artfynd/A 40059-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128602400</v>
       </c>
       <c r="B2" t="n">
-        <v>96242</v>
+        <v>96247</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40059-2025 artfynd.xlsx
+++ b/artfynd/A 40059-2025 artfynd.xlsx
@@ -1384,7 +1384,7 @@
         <v>128806558</v>
       </c>
       <c r="B8" t="n">
-        <v>97522</v>
+        <v>97527</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 40059-2025 artfynd.xlsx
+++ b/artfynd/A 40059-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128602400</v>
       </c>
       <c r="B2" t="n">
-        <v>96247</v>
+        <v>96255</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>128806558</v>
       </c>
       <c r="B8" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 40059-2025 artfynd.xlsx
+++ b/artfynd/A 40059-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>128628492</v>
       </c>
       <c r="B4" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>128642834</v>
       </c>
       <c r="B5" t="n">
-        <v>57028</v>
+        <v>57030</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>128642757</v>
       </c>
       <c r="B6" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128642844</v>
       </c>
       <c r="B7" t="n">
-        <v>58400</v>
+        <v>58402</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>128806558</v>
       </c>
       <c r="B8" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 40059-2025 artfynd.xlsx
+++ b/artfynd/A 40059-2025 artfynd.xlsx
@@ -1384,7 +1384,7 @@
         <v>128806558</v>
       </c>
       <c r="B8" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 40059-2025 artfynd.xlsx
+++ b/artfynd/A 40059-2025 artfynd.xlsx
@@ -1384,7 +1384,7 @@
         <v>128806558</v>
       </c>
       <c r="B8" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 40059-2025 artfynd.xlsx
+++ b/artfynd/A 40059-2025 artfynd.xlsx
@@ -1384,7 +1384,7 @@
         <v>128806558</v>
       </c>
       <c r="B8" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 40059-2025 artfynd.xlsx
+++ b/artfynd/A 40059-2025 artfynd.xlsx
@@ -1384,7 +1384,7 @@
         <v>128806558</v>
       </c>
       <c r="B8" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 40059-2025 artfynd.xlsx
+++ b/artfynd/A 40059-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,49 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128602400</v>
+        <v>128599917</v>
       </c>
       <c r="B2" t="n">
-        <v>96255</v>
+        <v>92147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>1101</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nedre slänten 1, Ö om Funtamosse, Vg</t>
+          <t>Kant mot nyckelbiotop, Ö om Funtamosse, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>343078</v>
+        <v>343130</v>
       </c>
       <c r="R2" t="n">
-        <v>6435210</v>
+        <v>6435201</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -744,22 +751,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:55</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På gammal stubbe, troligen gran. Hjälp med artbestämning via Facebook-gruppen Svamp-klapp.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128606867</v>
+        <v>128602400</v>
       </c>
       <c r="B3" t="n">
-        <v>56913</v>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,42 +810,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Översta hällen, Ö om Funtamosse, Vg</t>
+          <t>Nedre slänten 1, Ö om Funtamosse, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>343216</v>
+        <v>343078</v>
       </c>
       <c r="R3" t="n">
-        <v>6435145</v>
+        <v>6435210</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -865,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,12 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre spillning. Den andra bildens tjocka klunsar får mig att undra om det kan vara gammal spelskit, men är väl omöjligt att avgöra.</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,6 +892,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -907,14 +911,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128628492</v>
+        <v>128624053</v>
       </c>
       <c r="B4" t="n">
-        <v>57722</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -935,14 +939,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -985,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -995,12 +999,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Torr granstubbe med spillkråkehack, i spännande stenformation.</t>
+          <t>En spillkråka var mycket aktiv i området, flög fram och åter och ropade. Ett par turer till mosseskogen tvärsöver Funtamosse åt väster, och mycket aktiv 100-200 meter söderut, där den också trummade. Den passerade flera gånger nära denna position, slog till alldeles upp i slänten kanske 30 m åt öster, och nära norrut i nyckelbiotopen.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128642834</v>
+        <v>128816596</v>
       </c>
       <c r="B5" t="n">
-        <v>57030</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1038,16 +1042,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100065</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1055,28 +1059,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Funtamosse öster 2, Risveden, Vg</t>
+          <t>Strandskogen 2, Ö om Funtamosse, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>343152</v>
+        <v>343052</v>
       </c>
       <c r="R5" t="n">
-        <v>6435175</v>
+        <v>6435204</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,27 +1108,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>3 flockar</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,72 +1138,68 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lennart Gustafson</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lennart Gustafson</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128642757</v>
+        <v>128642834</v>
       </c>
       <c r="B6" t="n">
-        <v>57885</v>
+        <v>57258</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100065</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Funtamosse öster 1, Risveden, Vg</t>
+          <t>Funtamosse öster 2, Risveden, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>343076</v>
+        <v>343152</v>
       </c>
       <c r="R6" t="n">
-        <v>6435192</v>
+        <v>6435175</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1240,6 +1239,11 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>3 flockar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128642844</v>
+        <v>128606867</v>
       </c>
       <c r="B7" t="n">
-        <v>58402</v>
+        <v>57141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,21 +1281,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103044</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1299,23 +1303,23 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Funtamosse öster 2, Risveden, Vg</t>
+          <t>Översta hällen, Ö om Funtamosse, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>343152</v>
+        <v>343216</v>
       </c>
       <c r="R7" t="n">
-        <v>6435175</v>
+        <v>6435145</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1339,22 +1343,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre spillning. Den andra bildens tjocka klunsar får mig att undra om det kan vara gammal spelskit, men är väl omöjligt att avgöra.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1369,61 +1378,69 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lennart Gustafson</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lennart Gustafson</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128806558</v>
+        <v>128642757</v>
       </c>
       <c r="B8" t="n">
-        <v>97576</v>
+        <v>58114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fuktdråg 2, Ö om Funtamosse, Vg</t>
+          <t>Funtamosse öster 1, Risveden, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>343062</v>
+        <v>343076</v>
       </c>
       <c r="R8" t="n">
-        <v>6435187</v>
+        <v>6435192</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1450,22 +1467,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,22 +1491,248 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Lennart Gustafson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lennart Gustafson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128642844</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Funtamosse öster 2, Risveden, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>343152</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6435175</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Lennart Gustafson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Lennart Gustafson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128806558</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Fuktdråg 2, Ö om Funtamosse, Vg</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>343062</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6435187</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Ola Freijd</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Ola Freijd</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40059-2025 artfynd.xlsx
+++ b/artfynd/A 40059-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128599917</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,6 +918,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128602400</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1028,6 +1043,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624053</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1147,6 +1167,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128816596</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1267,6 +1292,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128642834</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1387,6 +1417,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128606867</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1506,6 +1541,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128642757</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1621,6 +1661,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128642844</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1733,8 +1778,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128806558</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>